--- a/Result/profitability/1439.xlsx
+++ b/Result/profitability/1439.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>0.6187500000000001</v>
+        <v>0.6325000000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>34.25125</v>
+        <v>30.37125</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.08</v>
       </c>
       <c r="M3" t="n">
-        <v>0.58125</v>
+        <v>0.5550000000000002</v>
       </c>
       <c r="N3" t="n">
-        <v>28.5275</v>
+        <v>23.10625</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.05</v>
       </c>
       <c r="M4" t="n">
-        <v>0.5000000000000001</v>
+        <v>0.4700000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>21.39625</v>
+        <v>20.505</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
         <v>0.4125000000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>19.05</v>
+        <v>18.465</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.09</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3625000000000002</v>
+        <v>0.3150000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>17.215</v>
+        <v>17.10625</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.09</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2650000000000001</v>
+        <v>0.1862500000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>14.90375</v>
+        <v>14.79625</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.1</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1375000000000001</v>
+        <v>0.1250000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>12.81625</v>
+        <v>12.095</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1521,7 +1521,7 @@
         <v>0.06625000000000011</v>
       </c>
       <c r="N9" t="n">
-        <v>9.70875</v>
+        <v>9.708749999999998</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1648,7 +1648,7 @@
         <v>0.05375000000000011</v>
       </c>
       <c r="N10" t="n">
-        <v>8.59625</v>
+        <v>8.596250000000001</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -9834,6 +9834,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1439</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>40</v>
+      </c>
+      <c r="D75" t="n">
+        <v>30</v>
+      </c>
+      <c r="E75" t="n">
+        <v>10</v>
+      </c>
+      <c r="F75" t="n">
+        <v>24.35</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-5</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-12.84%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>61</v>
+      </c>
+      <c r="J75" t="n">
+        <v>56</v>
+      </c>
+      <c r="K75" t="n">
+        <v>45</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.6712500000000001</v>
+      </c>
+      <c r="N75" t="n">
+        <v>36.065</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.09999999999999998</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.1694915254237288</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-5.77</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.1915670650730411</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-4.68</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.1612125387530141</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
